--- a/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
   <si>
     <t>TC ID</t>
   </si>
@@ -95,6 +95,9 @@
     <t>Odometer</t>
   </si>
   <si>
+    <t>Payout Odometer</t>
+  </si>
+  <si>
     <t>Fuel Provider</t>
   </si>
   <si>
@@ -155,10 +158,25 @@
     <t>Remittance Advice</t>
   </si>
   <si>
+    <t>EOL Date</t>
+  </si>
+  <si>
+    <t>Payout Amount</t>
+  </si>
+  <si>
+    <t>Payout Valid-to Date</t>
+  </si>
+  <si>
+    <t>Lease Type</t>
+  </si>
+  <si>
     <t>TC001</t>
   </si>
   <si>
-    <t>Fuel Card</t>
+    <t>Early Termination</t>
+  </si>
+  <si>
+    <t>20184</t>
   </si>
   <si>
     <t>N/A</t>
@@ -167,7 +185,13 @@
     <t>Lost</t>
   </si>
   <si>
-    <t>REQ-689</t>
+    <t>21 May 2026</t>
+  </si>
+  <si>
+    <t>17 Mar 2026</t>
+  </si>
+  <si>
+    <t>REQ-757</t>
   </si>
   <si>
     <t>ORIX Motorpass</t>
@@ -182,39 +206,42 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Stewart</t>
-  </si>
-  <si>
-    <t>30/10/1997</t>
-  </si>
-  <si>
-    <t>0499999999</t>
-  </si>
-  <si>
-    <t>visionpro101@gmail.com.test</t>
+    <t>Darryn</t>
+  </si>
+  <si>
+    <t>Grumley</t>
+  </si>
+  <si>
+    <t>29/04/1983</t>
+  </si>
+  <si>
+    <t>0494488844</t>
+  </si>
+  <si>
+    <t>darryn.j.grumley@exxonmobil.com.test</t>
   </si>
   <si>
     <t>Your Residential Address *</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CPK418</t>
-  </si>
-  <si>
-    <t>VOLVO C40</t>
-  </si>
-  <si>
-    <t>25 Sept 2026</t>
+    <t>ESSO Australia Pty Ltd</t>
+  </si>
+  <si>
+    <t>DAZ734</t>
+  </si>
+  <si>
+    <t>MAZDA CX-60</t>
+  </si>
+  <si>
+    <t>30 Aug 2029</t>
   </si>
   <si>
     <t>C:\Automation\Test cases Novated App\Filestoupload\RemittanceAdvice.pdf</t>
   </si>
   <si>
+    <t>12 Jun 2026</t>
+  </si>
+  <si>
     <t>TC002</t>
   </si>
   <si>
@@ -291,6 +318,15 @@
   </si>
   <si>
     <t>No Number Info</t>
+  </si>
+  <si>
+    <t>${TC001.EOL Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Payout Amount}</t>
+  </si>
+  <si>
+    <t>${TC001.Payout Valid-to Date}</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
@@ -1323,14 +1359,18 @@
     <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
     <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
-    <col min="18" max="22" width="19.1083333333333" customWidth="1"/>
-    <col min="23" max="23" width="20.7" customWidth="1"/>
-    <col min="24" max="24" width="24.6" customWidth="1"/>
-    <col min="25" max="25" width="29.8" customWidth="1"/>
-    <col min="26" max="27" width="24.5" customWidth="1"/>
+    <col min="18" max="23" width="19.1083333333333" customWidth="1"/>
+    <col min="24" max="24" width="20.7" customWidth="1"/>
+    <col min="25" max="25" width="24.6" customWidth="1"/>
+    <col min="26" max="26" width="29.8" customWidth="1"/>
+    <col min="27" max="28" width="24.5" customWidth="1"/>
+    <col min="36" max="36" width="26.6" customWidth="1"/>
+    <col min="43" max="44" width="12.4" customWidth="1"/>
+    <col min="45" max="45" width="14.6" customWidth="1"/>
+    <col min="46" max="46" width="16.7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="69" spans="1:42">
+    <row r="1" s="1" customFormat="1" ht="69" spans="1:47">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1457,240 +1497,288 @@
       <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="AQ1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="124.2" spans="1:42">
+    <row r="2" s="2" customFormat="1" ht="82.8" spans="1:47">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="6">
+        <f>C2+1</f>
+        <v>20185</v>
+      </c>
+      <c r="E2" s="6">
+        <f>D2</f>
+        <v>20185</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="U2" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>0 km</v>
-      </c>
-      <c r="W2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7" t="s">
+        <v>20,185 km</v>
+      </c>
+      <c r="W2" s="7" t="str">
+        <f>TEXT(C2,"#,##0")&amp;" km"</f>
+        <v>20,184 km</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF2" s="7" t="str">
+        <f>_xlfn.CONCAT(AD2," ",AE2)</f>
+        <v>Darryn Grumley</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL2" s="7" t="str">
+        <f>AN2&amp;" - "&amp;AM2</f>
+        <v>MAZDA CX-60 - DAZ734</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS2" s="7"/>
+      <c r="AT2" s="7"/>
+      <c r="AU2" s="7"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:47">
+      <c r="A3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE2" s="7" t="str">
-        <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>David Stewart</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ2" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK2" s="7" t="str">
-        <f>AM2&amp;" - "&amp;AL2</f>
-        <v>VOLVO C40 - CPK418</v>
-      </c>
-      <c r="AL2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AM2" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AO2" s="7"/>
-      <c r="AP2" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:42">
-      <c r="A3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="W3" s="4"/>
       <c r="X3" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AK3" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AN3" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP3" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="AP3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ3" s="4"/>
+      <c r="AR3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AS3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AU3" s="4"/>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:47">
       <c r="E5" s="8"/>
     </row>
-    <row r="10" spans="1:42">
+    <row r="10" spans="1:47">
       <c r="U10" s="9"/>
     </row>
   </sheetData>
